--- a/model/dataset/dataset.xlsx
+++ b/model/dataset/dataset.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YG_Travel\model\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2825E44E-41B4-478D-A2C7-AD246431A217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C279072-110E-48E1-ADB0-2D97445BCBC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A104E34A-024A-424E-93D8-B57E04A9C6C5}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="221">
   <si>
     <t>STT</t>
   </si>
@@ -667,12 +667,6 @@
     <t>Núi Cấm</t>
   </si>
   <si>
-    <t>là một khu rừng và khu du lịch sinh thái nằm trên địa bàn  tỉnh An Giang. Đây là rừng ngập nước tiêu biểu cho vùng Tây sông Hậu, là nơi sinh sống của nhiều loài động vật và thực vật thuộc hệ thống rừng đặc dụng Việt Nam và cũng là khu rừng tràm đẹp nhất và nổi tiếng nhất Việt Nam</t>
-  </si>
-  <si>
-    <t>là một ngọn núi ở An Giang, cách Long Xuyên khoảng 90km. Với độ cao 705m so với mực nước biển và diện tích trải dài hơn 28.600ha, với những đặc điểm địa chất độc đáo, kết hợp giữa rừng rậm và đá núi tạo nên cảnh quan hoang sơ nhưng hùng vĩ. Núi Cấm không chỉ là ngọn núi cao nhất trong dãy Thất Sơn mà còn là một trong những địa điểm du lịch tâm linh nổi tiếng nhất miền Tây Nam Bộ.</t>
-  </si>
-  <si>
     <t>Hòn Khô</t>
   </si>
   <si>
@@ -698,13 +692,28 @@
   </si>
   <si>
     <t>Tây Ninh</t>
+  </si>
+  <si>
+    <t>Là một khu rừng và khu du lịch sinh thái nằm trên địa bàn  tỉnh An Giang. Đây là rừng ngập nước tiêu biểu cho vùng Tây sông Hậu, là nơi sinh sống của nhiều loài động vật và thực vật thuộc hệ thống rừng đặc dụng Việt Nam và cũng là khu rừng tràm đẹp nhất và nổi tiếng nhất Việt Nam</t>
+  </si>
+  <si>
+    <t>Là một ngọn núi ở An Giang, cách Long Xuyên khoảng 90km. Với độ cao 705m so với mực nước biển và diện tích trải dài hơn 28.600ha, với những đặc điểm địa chất độc đáo, kết hợp giữa rừng rậm và đá núi tạo nên cảnh quan hoang sơ nhưng hùng vĩ. Núi Cấm không chỉ là ngọn núi cao nhất trong dãy Thất Sơn mà còn là một trong những địa điểm du lịch tâm linh nổi tiếng nhất miền Tây Nam Bộ.</t>
+  </si>
+  <si>
+    <t>Được mệnh danh là Đảo Ngọc lớn nhất Việt Nam với nhiều bãi biển đẹp và hơn 20 hòn đảo lớn nhỏ khác nhau tạo thành một quần thể đáo xanh tươi, thơ mộng ngay giữa đại dương. Eo biển xanh Phú Quốc được ví như Vịnh Hawai trữ tình nổi tiếng của Mĩ với những bờ biển đẹp vào bậc nhất Việt Nam.</t>
+  </si>
+  <si>
+    <t>Một khu rừng ngập mặn với hệ sinh thái phong phú và vẻ đẹp hùng vĩ  hoang sơ. Được bao bọc bởi thiên nhiên và lịch sử lâu đời, là điểm đến cho những ai đang tìm kiếm sự bình yên và cũng là nơi để trở về với nguồn cội</t>
+  </si>
+  <si>
+    <t>Một di tích lịch sử nằm giữa lòng núi rừng hùng vĩ với vẻ đẹp tĩnh lặng và trang nghiêm. Được bao bọc bởi bóng mát của núi Hòn Đất và tiếng sóng biển rì rào, nơi đây không chỉ là điểm đến cho những ai tìm kiếm sự thanh tịnh trong tâm hồn mà còn là nơi để tri ân, trở về với những giá trị hào hùng của nguồn cội và lòng yêu nước bất khuất.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -735,6 +744,12 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF343A40"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -756,7 +771,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -775,6 +790,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1148,7 +1164,7 @@
         <v>184</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="E2" s="2"/>
     </row>
@@ -1163,7 +1179,7 @@
         <v>206</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -1177,7 +1193,9 @@
       <c r="C4" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="2" t="s">
+        <v>218</v>
+      </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.35">
@@ -1190,7 +1208,9 @@
       <c r="C5" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" s="8" t="s">
+        <v>219</v>
+      </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5" ht="18" x14ac:dyDescent="0.35">
@@ -1203,7 +1223,9 @@
       <c r="C6" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" s="2" t="s">
+        <v>220</v>
+      </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5" ht="18" x14ac:dyDescent="0.35">
@@ -1864,7 +1886,7 @@
         <v>140</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
@@ -3138,7 +3160,7 @@
         <v>98</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D155" s="2"/>
       <c r="E155" s="2"/>
@@ -3177,7 +3199,7 @@
         <v>170</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D158" s="2"/>
       <c r="E158" s="2"/>
@@ -3382,10 +3404,10 @@
         <v>173</v>
       </c>
       <c r="B174" s="7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C174" s="7" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D174" s="7"/>
       <c r="E174" s="7"/>
@@ -3395,10 +3417,10 @@
         <v>174</v>
       </c>
       <c r="B175" s="7" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C175" s="7" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D175" s="7"/>
       <c r="E175" s="7"/>
@@ -3408,10 +3430,10 @@
         <v>175</v>
       </c>
       <c r="B176" s="7" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C176" s="7" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D176" s="7"/>
       <c r="E176" s="7"/>
@@ -3421,10 +3443,10 @@
         <v>176</v>
       </c>
       <c r="B177" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C177" s="7" t="s">
         <v>215</v>
-      </c>
-      <c r="C177" s="7" t="s">
-        <v>217</v>
       </c>
       <c r="D177" s="7"/>
       <c r="E177" s="7"/>
@@ -3434,10 +3456,10 @@
         <v>177</v>
       </c>
       <c r="B178" s="7" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C178" s="7" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D178" s="7"/>
       <c r="E178" s="7"/>
